--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9647EE2B-B695-49E3-A196-92576B301975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AF2ADB-7EEF-43D0-8DE1-625754B98F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -491,11 +491,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{class:"RemoveBuffById",values:[1,2],probability:10000},class:"RecureWoundedTroops",probability:10000,values:[20,30], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CommonMethod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"RemoveBuffById",values:[1,2],probability:10000},{class:"RecureWoundedTroops",probability:10000,values:[20,30], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1390,7 +1390,7 @@
         <v>100</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>105</v>
@@ -3094,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T30" s="2" t="s">
         <v>6</v>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AF2ADB-7EEF-43D0-8DE1-625754B98F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A608777-0556-4F20-9081-555B56137470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="128">
   <si>
     <t>备注:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -470,20 +470,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{class:"Burn",probability:5000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"Burn",probability:5000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-  </si>
-  <si>
-    <t>[{class:"Burn",probability:5000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"Burn",probability:5000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{class:"AddBuff",buffId:1,probability:5000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:1,probability:5000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{class:"Burn",probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"Burn",probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-  </si>
-  <si>
     <t>[{class:"AddBuff",buffId:2,probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:2,probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
   </si>
   <si>
@@ -496,6 +486,14 @@
   </si>
   <si>
     <t>[{class:"RemoveBuffById",values:[1,2],probability:10000},{class:"RecureWoundedTroops",probability:10000,values:[20,30], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"SetFire",probability:5000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"SetFire",probability:5000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"SetFire",probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"SetFire",probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1390,7 +1388,7 @@
         <v>100</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>105</v>
@@ -1548,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>6</v>
@@ -1906,7 +1904,7 @@
         <v>2</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>6</v>
@@ -2334,7 +2332,7 @@
         <v>2</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="T19" s="2" t="s">
         <v>6</v>
@@ -2475,7 +2473,7 @@
         <v>1</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="T21" s="2" t="s">
         <v>6</v>
@@ -2619,7 +2617,7 @@
         <v>2</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="T23" s="2" t="s">
         <v>6</v>
@@ -2829,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="T26" s="2" t="s">
         <v>6</v>
@@ -2961,7 +2959,7 @@
         <v>1</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="T28" s="2" t="s">
         <v>6</v>
@@ -3027,7 +3025,7 @@
         <v>1</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="T29" s="2" t="s">
         <v>6</v>
@@ -3094,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="T30" s="2" t="s">
         <v>6</v>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A608777-0556-4F20-9081-555B56137470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411B48EF-300A-47A2-B468-DDD027F7F271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="131">
   <si>
     <t>备注:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -439,62 +439,74 @@
     <t>AmbushCriticalMethod</t>
   </si>
   <si>
+    <t>PutOutFireSuccessMethod</t>
+  </si>
+  <si>
+    <t>FalseReportSuccessMethod</t>
+  </si>
+  <si>
+    <t>DisturbSuccessMethod</t>
+  </si>
+  <si>
+    <t>CalmdownSuccessMethod</t>
+  </si>
+  <si>
+    <t>AmbushSuccessMethod</t>
+  </si>
+  <si>
+    <t>InfightingSuccessMethod</t>
+  </si>
+  <si>
+    <t>InfightingCriticalMethod</t>
+  </si>
+  <si>
+    <t>FireCriticalMethod</t>
+  </si>
+  <si>
+    <t>[{class:"PutoutFire",probability:10000}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"AddBuff",buffId:1,probability:5000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:1,probability:5000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"AddBuff",buffId:2,probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:2,probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+  </si>
+  <si>
+    <t>[{class:"AddBuff",buffId:1,probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:1,probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CommonMethod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"RemoveBuffById",values:[1,2],probability:10000},{class:"RecureWoundedTroops",probability:10000,values:[20,30], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"SetFire",probability:5000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"SetFire",probability:5000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"SetFire",probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"SetFire",probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>射程筛选逻辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rangeFilterMethod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>FireSuccessMethod</t>
-  </si>
-  <si>
-    <t>PutOutFireSuccessMethod</t>
-  </si>
-  <si>
-    <t>FalseReportSuccessMethod</t>
-  </si>
-  <si>
-    <t>DisturbSuccessMethod</t>
-  </si>
-  <si>
-    <t>CalmdownSuccessMethod</t>
-  </si>
-  <si>
-    <t>AmbushSuccessMethod</t>
-  </si>
-  <si>
-    <t>InfightingSuccessMethod</t>
-  </si>
-  <si>
-    <t>InfightingCriticalMethod</t>
-  </si>
-  <si>
-    <t>FireCriticalMethod</t>
-  </si>
-  <si>
-    <t>[{class:"PutoutFire",probability:10000}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"AddBuff",buffId:1,probability:5000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:1,probability:5000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"AddBuff",buffId:2,probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:2,probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-  </si>
-  <si>
-    <t>[{class:"AddBuff",buffId:1,probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:1,probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CommonMethod</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"RemoveBuffById",values:[1,2],probability:10000},{class:"RecureWoundedTroops",probability:10000,values:[20,30], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"SetFire",probability:5000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"SetFire",probability:5000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"SetFire",probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"SetFire",probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QRSLineMethod</t>
   </si>
 </sst>
 </file>
@@ -978,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
-  <dimension ref="A1:AH69"/>
+  <dimension ref="A1:AI69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.375" style="2" bestFit="1" customWidth="1"/>
@@ -988,27 +1000,29 @@
     <col min="6" max="6" width="10.5" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.75" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="255.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.75" style="2" customWidth="1"/>
-    <col min="21" max="21" width="20.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.25" style="2" customWidth="1"/>
-    <col min="28" max="28" width="70.5" style="2" customWidth="1"/>
-    <col min="29" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="16.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.25" style="2" customWidth="1"/>
+    <col min="11" max="11" width="21.875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="22.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="255.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.75" style="2" customWidth="1"/>
+    <col min="22" max="22" width="20.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="22" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.25" style="2" customWidth="1"/>
+    <col min="29" max="29" width="70.5" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="12" t="s">
         <v>9</v>
@@ -1039,43 +1053,43 @@
         <v>104</v>
       </c>
       <c r="L1" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="O1" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="P1" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="O1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="12" t="s">
+      <c r="Q1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="R1" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="S1" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="T1" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="U1" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="V1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="W1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="X1" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="X1" s="12" t="s">
-        <v>42</v>
       </c>
       <c r="Y1" s="12" t="s">
         <v>42</v>
@@ -1083,16 +1097,19 @@
       <c r="Z1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AA1" s="12"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="8"/>
-      <c r="AF1" s="6"/>
-      <c r="AG1" s="8"/>
-      <c r="AH1" s="6"/>
-    </row>
-    <row r="2" spans="1:34" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB1" s="12"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="8"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="6"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="6"/>
+    </row>
+    <row r="2" spans="1:35" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1121,16 +1138,17 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="2"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="14"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
-    </row>
-    <row r="3" spans="1:34" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AI2" s="2"/>
+    </row>
+    <row r="3" spans="1:35" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1163,51 +1181,53 @@
         <v>102</v>
       </c>
       <c r="L3" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="N3" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="P3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="X3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="Z3" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="AA3" s="7"/>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
       <c r="AD3" s="7"/>
@@ -1215,8 +1235,9 @@
       <c r="AF3" s="7"/>
       <c r="AG3" s="7"/>
       <c r="AH3" s="7"/>
-    </row>
-    <row r="4" spans="1:34" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AI3" s="7"/>
+    </row>
+    <row r="4" spans="1:35" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1251,31 +1272,31 @@
         <v>88</v>
       </c>
       <c r="L4" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="O4" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="P4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="Q4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="R4" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="S4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="R4" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="S4" s="13" t="s">
+      <c r="T4" s="13" t="s">
         <v>66</v>
-      </c>
-      <c r="T4" s="13" t="s">
-        <v>8</v>
       </c>
       <c r="U4" s="13" t="s">
         <v>8</v>
@@ -1295,9 +1316,12 @@
       <c r="Z4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AA4" s="15"/>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AA4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB4" s="15"/>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1326,18 +1350,15 @@
       <c r="K5" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="4">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
         <v>0</v>
       </c>
-      <c r="M5" s="4"/>
-      <c r="N5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O5" s="4">
-        <v>1</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>6</v>
+      <c r="O5" s="4"/>
+      <c r="P5" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="U5" s="2" t="s">
         <v>6</v>
@@ -1349,7 +1370,7 @@
         <v>6</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5" s="2" t="s">
         <v>7</v>
@@ -1357,13 +1378,16 @@
       <c r="Z5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA5" s="4"/>
-      <c r="AC5" s="4"/>
+      <c r="AA5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB5" s="4"/>
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
-      <c r="AG5" s="4"/>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AF5" s="4"/>
+      <c r="AH5" s="4"/>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1388,22 +1412,19 @@
         <v>100</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L6" s="4">
+      <c r="M6" s="4">
+        <v>2</v>
+      </c>
+      <c r="N6" s="4">
         <v>0</v>
       </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O6" s="4">
-        <v>2</v>
-      </c>
-      <c r="T6" s="2" t="s">
+      <c r="O6" s="4"/>
+      <c r="P6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="U6" s="2" t="s">
@@ -1416,7 +1437,7 @@
         <v>6</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6" s="2" t="s">
         <v>7</v>
@@ -1424,13 +1445,16 @@
       <c r="Z6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA6" s="4"/>
-      <c r="AC6" s="4"/>
+      <c r="AA6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB6" s="4"/>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
-      <c r="AG6" s="4"/>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AF6" s="4"/>
+      <c r="AH6" s="4"/>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1461,30 +1485,27 @@
       <c r="K7" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L7" s="4">
+      <c r="M7" s="4">
         <v>1</v>
       </c>
-      <c r="M7" s="4"/>
-      <c r="N7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O7" s="4">
+      <c r="N7" s="4">
         <v>1</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="O7" s="4"/>
+      <c r="P7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>7</v>
@@ -1498,13 +1519,16 @@
       <c r="Z7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA7" s="4"/>
-      <c r="AC7" s="4"/>
+      <c r="AA7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB7" s="4"/>
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
-      <c r="AG7" s="4"/>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AF7" s="4"/>
+      <c r="AH7" s="4"/>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1535,27 +1559,24 @@
       <c r="K8" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L8" s="4">
+      <c r="M8" s="4">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4">
         <v>2</v>
       </c>
-      <c r="M8" s="4"/>
-      <c r="N8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O8" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>6</v>
+      <c r="O8" s="4"/>
+      <c r="P8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>7</v>
@@ -1569,13 +1590,16 @@
       <c r="Z8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA8" s="4"/>
-      <c r="AC8" s="4"/>
+      <c r="AA8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB8" s="4"/>
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
-      <c r="AG8" s="4"/>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AF8" s="4"/>
+      <c r="AH8" s="4"/>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -1606,30 +1630,27 @@
       <c r="K9" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L9" s="4">
+      <c r="M9" s="4">
+        <v>1</v>
+      </c>
+      <c r="N9" s="4">
         <v>3</v>
       </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O9" s="4">
-        <v>1</v>
-      </c>
-      <c r="R9" s="2" t="s">
+      <c r="O9" s="4"/>
+      <c r="P9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="T9" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="U9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>7</v>
@@ -1643,13 +1664,16 @@
       <c r="Z9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA9" s="4"/>
-      <c r="AC9" s="4"/>
+      <c r="AA9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB9" s="4"/>
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
-      <c r="AG9" s="4"/>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AF9" s="4"/>
+      <c r="AH9" s="4"/>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -1680,27 +1704,24 @@
       <c r="K10" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L10" s="4">
+      <c r="M10" s="4">
         <v>1</v>
       </c>
-      <c r="M10" s="4"/>
-      <c r="N10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O10" s="4">
+      <c r="N10" s="4">
         <v>1</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="O10" s="4"/>
+      <c r="P10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="T10" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="U10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>7</v>
@@ -1714,13 +1735,16 @@
       <c r="Z10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA10" s="4"/>
-      <c r="AC10" s="4"/>
+      <c r="AA10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB10" s="4"/>
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
-      <c r="AG10" s="4"/>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AF10" s="4"/>
+      <c r="AH10" s="4"/>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -1751,27 +1775,24 @@
       <c r="K11" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L11" s="4">
+      <c r="M11" s="4">
+        <v>1</v>
+      </c>
+      <c r="N11" s="4">
         <v>2</v>
       </c>
-      <c r="M11" s="4"/>
-      <c r="N11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O11" s="4">
-        <v>1</v>
-      </c>
+      <c r="O11" s="4"/>
       <c r="P11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T11" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="U11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>7</v>
@@ -1785,13 +1806,16 @@
       <c r="Z11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA11" s="4"/>
-      <c r="AC11" s="4"/>
+      <c r="AA11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB11" s="4"/>
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
-      <c r="AG11" s="4"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AF11" s="4"/>
+      <c r="AH11" s="4"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -1822,27 +1846,24 @@
       <c r="K12" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L12" s="4">
+      <c r="M12" s="4">
+        <v>1</v>
+      </c>
+      <c r="N12" s="4">
         <v>3</v>
       </c>
-      <c r="M12" s="4"/>
-      <c r="N12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O12" s="4">
-        <v>1</v>
-      </c>
+      <c r="O12" s="4"/>
       <c r="P12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="T12" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="U12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>7</v>
@@ -1856,13 +1877,16 @@
       <c r="Z12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA12" s="4"/>
-      <c r="AC12" s="4"/>
+      <c r="AA12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB12" s="4"/>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
-      <c r="AG12" s="4"/>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AF12" s="4"/>
+      <c r="AH12" s="4"/>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -1893,21 +1917,18 @@
       <c r="K13" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L13" s="4">
+      <c r="M13" s="4">
+        <v>2</v>
+      </c>
+      <c r="N13" s="4">
         <v>1</v>
       </c>
-      <c r="M13" s="4"/>
-      <c r="N13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O13" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>6</v>
+      <c r="O13" s="4"/>
+      <c r="P13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="U13" s="2" t="s">
         <v>6</v>
@@ -1919,7 +1940,7 @@
         <v>6</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13" s="2" t="s">
         <v>7</v>
@@ -1927,13 +1948,16 @@
       <c r="Z13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA13" s="4"/>
-      <c r="AC13" s="4"/>
+      <c r="AA13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB13" s="4"/>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
-      <c r="AG13" s="4"/>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AF13" s="4"/>
+      <c r="AH13" s="4"/>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -1964,22 +1988,22 @@
       <c r="K14" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="M14" s="4">
         <v>2</v>
       </c>
-      <c r="M14" s="4"/>
-      <c r="N14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O14" s="4">
+      <c r="N14" s="4">
         <v>2</v>
       </c>
+      <c r="O14" s="4"/>
       <c r="P14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="T14" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="U14" s="2" t="s">
         <v>6</v>
       </c>
@@ -1990,7 +2014,7 @@
         <v>6</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14" s="2" t="s">
         <v>7</v>
@@ -1998,13 +2022,16 @@
       <c r="Z14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA14" s="4"/>
-      <c r="AC14" s="4"/>
+      <c r="AA14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB14" s="4"/>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
-      <c r="AG14" s="4"/>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AF14" s="4"/>
+      <c r="AH14" s="4"/>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2035,22 +2062,19 @@
       <c r="K15" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L15" s="4">
+      <c r="M15" s="4">
+        <v>2</v>
+      </c>
+      <c r="N15" s="4">
         <v>3</v>
       </c>
-      <c r="M15" s="4"/>
-      <c r="N15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O15" s="4">
-        <v>2</v>
-      </c>
+      <c r="O15" s="4"/>
       <c r="P15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="T15" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="U15" s="2" t="s">
         <v>6</v>
       </c>
@@ -2061,7 +2085,7 @@
         <v>6</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y15" s="2" t="s">
         <v>7</v>
@@ -2069,13 +2093,16 @@
       <c r="Z15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA15" s="4"/>
-      <c r="AC15" s="4"/>
+      <c r="AA15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB15" s="4"/>
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
-      <c r="AG15" s="4"/>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AF15" s="4"/>
+      <c r="AH15" s="4"/>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2106,27 +2133,24 @@
       <c r="K16" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L16" s="4">
+      <c r="M16" s="4">
         <v>1</v>
       </c>
-      <c r="M16" s="4"/>
-      <c r="N16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O16" s="4">
+      <c r="N16" s="4">
         <v>1</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="O16" s="4"/>
+      <c r="P16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S16" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="T16" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="U16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>7</v>
@@ -2140,13 +2164,16 @@
       <c r="Z16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA16" s="4"/>
-      <c r="AC16" s="4"/>
+      <c r="AA16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB16" s="4"/>
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
-      <c r="AG16" s="4"/>
-    </row>
-    <row r="17" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF16" s="4"/>
+      <c r="AH16" s="4"/>
+    </row>
+    <row r="17" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2177,27 +2204,24 @@
       <c r="K17" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L17" s="4">
+      <c r="M17" s="4">
+        <v>1</v>
+      </c>
+      <c r="N17" s="4">
         <v>2</v>
       </c>
-      <c r="M17" s="4"/>
-      <c r="N17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O17" s="4">
-        <v>1</v>
-      </c>
-      <c r="R17" s="2" t="s">
+      <c r="O17" s="4"/>
+      <c r="P17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S17" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="T17" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="U17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W17" s="2" t="s">
         <v>7</v>
@@ -2211,13 +2235,16 @@
       <c r="Z17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA17" s="4"/>
-      <c r="AC17" s="4"/>
+      <c r="AA17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB17" s="4"/>
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
-      <c r="AG17" s="4"/>
-    </row>
-    <row r="18" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF17" s="4"/>
+      <c r="AH17" s="4"/>
+    </row>
+    <row r="18" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2248,27 +2275,24 @@
       <c r="K18" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L18" s="4">
+      <c r="M18" s="4">
+        <v>1</v>
+      </c>
+      <c r="N18" s="4">
         <v>3</v>
       </c>
-      <c r="M18" s="4"/>
-      <c r="N18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O18" s="4">
-        <v>1</v>
-      </c>
-      <c r="R18" s="2" t="s">
+      <c r="O18" s="4"/>
+      <c r="P18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S18" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="T18" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="U18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W18" s="2" t="s">
         <v>7</v>
@@ -2282,13 +2306,16 @@
       <c r="Z18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA18" s="4"/>
-      <c r="AC18" s="4"/>
+      <c r="AA18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB18" s="4"/>
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
-      <c r="AG18" s="4"/>
-    </row>
-    <row r="19" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF18" s="4"/>
+      <c r="AH18" s="4"/>
+    </row>
+    <row r="19" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2319,35 +2346,32 @@
       <c r="K19" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L19" s="4">
+      <c r="M19" s="4">
+        <v>2</v>
+      </c>
+      <c r="N19" s="4">
         <v>0</v>
       </c>
-      <c r="M19" s="4">
-        <v>7</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="O19" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19" s="2" t="s">
         <v>7</v>
@@ -2355,12 +2379,15 @@
       <c r="Z19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC19" s="4"/>
+      <c r="AA19" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
-      <c r="AG19" s="4"/>
-    </row>
-    <row r="20" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF19" s="4"/>
+      <c r="AH19" s="4"/>
+    </row>
+    <row r="20" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -2391,19 +2418,16 @@
       <c r="K20" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L20" s="4">
+      <c r="M20" s="4">
+        <v>1</v>
+      </c>
+      <c r="N20" s="4">
         <v>0</v>
       </c>
-      <c r="M20" s="4">
-        <v>6</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="O20" s="4">
-        <v>1</v>
-      </c>
-      <c r="T20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="U20" s="2" t="s">
@@ -2413,10 +2437,10 @@
         <v>7</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20" s="2" t="s">
         <v>7</v>
@@ -2424,12 +2448,15 @@
       <c r="Z20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC20" s="4"/>
+      <c r="AA20" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AD20" s="4"/>
       <c r="AE20" s="4"/>
-      <c r="AG20" s="4"/>
-    </row>
-    <row r="21" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF20" s="4"/>
+      <c r="AH20" s="4"/>
+    </row>
+    <row r="21" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -2460,35 +2487,32 @@
       <c r="K21" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L21" s="4">
+      <c r="M21" s="4">
+        <v>1</v>
+      </c>
+      <c r="N21" s="4">
         <v>0</v>
       </c>
-      <c r="M21" s="4">
+      <c r="O21" s="4">
         <v>9</v>
       </c>
-      <c r="N21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O21" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>6</v>
+      <c r="P21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="U21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="V21" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21" s="2" t="s">
         <v>7</v>
@@ -2496,12 +2520,15 @@
       <c r="Z21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC21" s="4"/>
+      <c r="AA21" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AD21" s="4"/>
       <c r="AE21" s="4"/>
-      <c r="AG21" s="4"/>
-    </row>
-    <row r="22" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF21" s="4"/>
+      <c r="AH21" s="4"/>
+    </row>
+    <row r="22" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -2532,24 +2559,21 @@
       <c r="K22" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L22" s="4">
+      <c r="M22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N22" s="4">
         <v>0</v>
       </c>
-      <c r="M22" s="4">
+      <c r="O22" s="4">
         <v>8</v>
       </c>
-      <c r="N22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O22" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="P22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q22" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="T22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="U22" s="2" t="s">
         <v>6</v>
       </c>
@@ -2560,7 +2584,7 @@
         <v>6</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y22" s="2" t="s">
         <v>7</v>
@@ -2568,12 +2592,15 @@
       <c r="Z22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC22" s="4"/>
+      <c r="AA22" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AD22" s="4"/>
       <c r="AE22" s="4"/>
-      <c r="AG22" s="4"/>
-    </row>
-    <row r="23" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF22" s="4"/>
+      <c r="AH22" s="4"/>
+    </row>
+    <row r="23" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -2604,23 +2631,20 @@
       <c r="K23" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L23" s="4">
+      <c r="M23" s="4">
+        <v>2</v>
+      </c>
+      <c r="N23" s="4">
         <v>1</v>
       </c>
-      <c r="M23" s="4">
+      <c r="O23" s="4">
         <v>10</v>
       </c>
-      <c r="N23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O23" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>6</v>
+      <c r="P23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="U23" s="2" t="s">
         <v>6</v>
@@ -2632,7 +2656,7 @@
         <v>6</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23" s="2" t="s">
         <v>7</v>
@@ -2640,12 +2664,15 @@
       <c r="Z23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC23" s="4"/>
+      <c r="AA23" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AD23" s="4"/>
       <c r="AE23" s="4"/>
-      <c r="AG23" s="4"/>
-    </row>
-    <row r="24" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF23" s="4"/>
+      <c r="AH23" s="4"/>
+    </row>
+    <row r="24" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -2676,24 +2703,21 @@
       <c r="K24" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L24" s="4">
+      <c r="M24" s="4">
+        <v>1</v>
+      </c>
+      <c r="N24" s="4">
         <v>2</v>
       </c>
-      <c r="M24" s="4">
+      <c r="O24" s="4">
         <v>11</v>
       </c>
-      <c r="N24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O24" s="4">
-        <v>1</v>
-      </c>
-      <c r="R24" s="2" t="s">
+      <c r="P24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S24" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="T24" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="U24" s="2" t="s">
         <v>6</v>
       </c>
@@ -2704,7 +2728,7 @@
         <v>6</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y24" s="2" t="s">
         <v>7</v>
@@ -2712,12 +2736,15 @@
       <c r="Z24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC24" s="4"/>
+      <c r="AA24" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AD24" s="4"/>
       <c r="AE24" s="4"/>
-      <c r="AG24" s="4"/>
-    </row>
-    <row r="25" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF24" s="4"/>
+      <c r="AH24" s="4"/>
+    </row>
+    <row r="25" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -2748,24 +2775,21 @@
       <c r="K25" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L25" s="4">
+      <c r="M25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N25" s="4">
         <v>3</v>
       </c>
-      <c r="M25" s="4">
+      <c r="O25" s="4">
         <v>12</v>
       </c>
-      <c r="N25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="P25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q25" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="T25" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="U25" s="2" t="s">
         <v>6</v>
       </c>
@@ -2776,7 +2800,7 @@
         <v>6</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y25" s="2" t="s">
         <v>7</v>
@@ -2784,12 +2808,15 @@
       <c r="Z25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC25" s="4"/>
+      <c r="AA25" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AD25" s="4"/>
       <c r="AE25" s="4"/>
-      <c r="AG25" s="4"/>
-    </row>
-    <row r="26" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF25" s="4"/>
+      <c r="AH25" s="4"/>
+    </row>
+    <row r="26" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -2811,26 +2838,23 @@
         <v>0</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="L26" s="4">
+        <v>118</v>
+      </c>
+      <c r="M26" s="4">
+        <v>1</v>
+      </c>
+      <c r="N26" s="4">
         <v>0</v>
       </c>
-      <c r="M26" s="4"/>
-      <c r="N26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O26" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>6</v>
+      <c r="O26" s="4"/>
+      <c r="P26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="U26" s="2" t="s">
         <v>6</v>
@@ -2842,20 +2866,23 @@
         <v>6</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC26" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="AA26" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AD26" s="4"/>
       <c r="AE26" s="4"/>
-      <c r="AG26" s="4"/>
-    </row>
-    <row r="27" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF26" s="4"/>
+      <c r="AH26" s="4"/>
+    </row>
+    <row r="27" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -2877,26 +2904,23 @@
         <v>0</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="L27" s="4">
+      <c r="M27" s="4">
+        <v>1</v>
+      </c>
+      <c r="N27" s="4">
         <v>0</v>
       </c>
-      <c r="M27" s="4"/>
-      <c r="N27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O27" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="T27" s="2" t="s">
-        <v>6</v>
+      <c r="O27" s="4"/>
+      <c r="P27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="U27" s="2" t="s">
         <v>6</v>
@@ -2908,20 +2932,23 @@
         <v>6</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27" s="2" t="s">
         <v>7</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC27" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="AA27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="AD27" s="4"/>
       <c r="AE27" s="4"/>
-      <c r="AG27" s="4"/>
-    </row>
-    <row r="28" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF27" s="4"/>
+      <c r="AH27" s="4"/>
+    </row>
+    <row r="28" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -2943,26 +2970,23 @@
         <v>0</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="L28" s="4">
+      <c r="M28" s="4">
+        <v>1</v>
+      </c>
+      <c r="N28" s="4">
         <v>0</v>
       </c>
-      <c r="M28" s="4"/>
-      <c r="N28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O28" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>6</v>
+      <c r="O28" s="4"/>
+      <c r="P28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="U28" s="2" t="s">
         <v>6</v>
@@ -2971,7 +2995,7 @@
         <v>6</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X28" s="2" t="s">
         <v>7</v>
@@ -2982,12 +3006,15 @@
       <c r="Z28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC28" s="4"/>
+      <c r="AA28" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AD28" s="4"/>
       <c r="AE28" s="4"/>
-      <c r="AG28" s="4"/>
-    </row>
-    <row r="29" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF28" s="4"/>
+      <c r="AH28" s="4"/>
+    </row>
+    <row r="29" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3009,26 +3036,23 @@
         <v>0</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="L29" s="4">
+      <c r="M29" s="4">
+        <v>1</v>
+      </c>
+      <c r="N29" s="4">
         <v>0</v>
       </c>
-      <c r="M29" s="4"/>
-      <c r="N29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O29" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="T29" s="2" t="s">
-        <v>6</v>
+      <c r="O29" s="4"/>
+      <c r="P29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="U29" s="2" t="s">
         <v>6</v>
@@ -3037,7 +3061,7 @@
         <v>6</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X29" s="2" t="s">
         <v>7</v>
@@ -3048,13 +3072,16 @@
       <c r="Z29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA29" s="4"/>
-      <c r="AC29" s="4"/>
+      <c r="AA29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB29" s="4"/>
       <c r="AD29" s="4"/>
       <c r="AE29" s="4"/>
-      <c r="AG29" s="4"/>
-    </row>
-    <row r="30" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF29" s="4"/>
+      <c r="AH29" s="4"/>
+    </row>
+    <row r="30" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3076,26 +3103,23 @@
         <v>0</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="L30" s="4">
+      <c r="M30" s="4">
+        <v>1</v>
+      </c>
+      <c r="N30" s="4">
         <v>0</v>
       </c>
-      <c r="M30" s="4"/>
-      <c r="N30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O30" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>6</v>
+      <c r="O30" s="4"/>
+      <c r="P30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="U30" s="2" t="s">
         <v>6</v>
@@ -3104,7 +3128,7 @@
         <v>6</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X30" s="2" t="s">
         <v>7</v>
@@ -3113,15 +3137,18 @@
         <v>7</v>
       </c>
       <c r="Z30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA30" s="4"/>
-      <c r="AC30" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="AA30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB30" s="4"/>
       <c r="AD30" s="4"/>
       <c r="AE30" s="4"/>
-      <c r="AG30" s="4"/>
-    </row>
-    <row r="31" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF30" s="4"/>
+      <c r="AH30" s="4"/>
+    </row>
+    <row r="31" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -3143,22 +3170,19 @@
         <v>0</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="L31" s="4">
+      <c r="M31" s="4">
+        <v>1</v>
+      </c>
+      <c r="N31" s="4">
         <v>0</v>
       </c>
-      <c r="M31" s="4"/>
-      <c r="N31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O31" s="4">
-        <v>1</v>
-      </c>
-      <c r="T31" s="2" t="s">
+      <c r="O31" s="4"/>
+      <c r="P31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="U31" s="2" t="s">
@@ -3168,7 +3192,7 @@
         <v>6</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X31" s="2" t="s">
         <v>7</v>
@@ -3179,13 +3203,16 @@
       <c r="Z31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA31" s="4"/>
-      <c r="AC31" s="4"/>
+      <c r="AA31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB31" s="4"/>
       <c r="AD31" s="4"/>
       <c r="AE31" s="4"/>
-      <c r="AG31" s="4"/>
-    </row>
-    <row r="32" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF31" s="4"/>
+      <c r="AH31" s="4"/>
+    </row>
+    <row r="32" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -3207,22 +3234,19 @@
         <v>0</v>
       </c>
       <c r="J32" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K32" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="K32" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="L32" s="4">
+      <c r="M32" s="4">
+        <v>1</v>
+      </c>
+      <c r="N32" s="4">
         <v>0</v>
       </c>
-      <c r="M32" s="4"/>
-      <c r="N32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O32" s="4">
-        <v>1</v>
-      </c>
-      <c r="T32" s="2" t="s">
+      <c r="O32" s="4"/>
+      <c r="P32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="U32" s="2" t="s">
@@ -3232,7 +3256,7 @@
         <v>6</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X32" s="2" t="s">
         <v>7</v>
@@ -3243,13 +3267,16 @@
       <c r="Z32" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AA32" s="4"/>
-      <c r="AC32" s="4"/>
+      <c r="AA32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB32" s="4"/>
       <c r="AD32" s="4"/>
       <c r="AE32" s="4"/>
-      <c r="AG32" s="4"/>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF32" s="4"/>
+      <c r="AH32" s="4"/>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -3260,19 +3287,19 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
       <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
       <c r="O33" s="4"/>
-      <c r="T33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA33" s="4"/>
-      <c r="AC33" s="4"/>
+      <c r="U33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB33" s="4"/>
       <c r="AD33" s="4"/>
       <c r="AE33" s="4"/>
-      <c r="AG33" s="4"/>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF33" s="4"/>
+      <c r="AH33" s="4"/>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -3283,16 +3310,16 @@
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
       <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
       <c r="O34" s="4"/>
-      <c r="AA34" s="4"/>
-      <c r="AC34" s="4"/>
+      <c r="AB34" s="4"/>
       <c r="AD34" s="4"/>
       <c r="AE34" s="4"/>
-      <c r="AG34" s="4"/>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF34" s="4"/>
+      <c r="AH34" s="4"/>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -3303,16 +3330,16 @@
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
       <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
       <c r="O35" s="4"/>
-      <c r="AA35" s="4"/>
-      <c r="AC35" s="4"/>
+      <c r="AB35" s="4"/>
       <c r="AD35" s="4"/>
       <c r="AE35" s="4"/>
-      <c r="AG35" s="4"/>
-    </row>
-    <row r="36" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF35" s="4"/>
+      <c r="AH35" s="4"/>
+    </row>
+    <row r="36" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -3323,16 +3350,16 @@
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
       <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
       <c r="O36" s="4"/>
-      <c r="AA36" s="4"/>
-      <c r="AC36" s="4"/>
+      <c r="AB36" s="4"/>
       <c r="AD36" s="4"/>
       <c r="AE36" s="4"/>
-      <c r="AG36" s="4"/>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF36" s="4"/>
+      <c r="AH36" s="4"/>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -3343,16 +3370,16 @@
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
       <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
       <c r="O37" s="4"/>
-      <c r="AA37" s="4"/>
-      <c r="AC37" s="4"/>
+      <c r="AB37" s="4"/>
       <c r="AD37" s="4"/>
       <c r="AE37" s="4"/>
-      <c r="AG37" s="4"/>
-    </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF37" s="4"/>
+      <c r="AH37" s="4"/>
+    </row>
+    <row r="38" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -3363,16 +3390,16 @@
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
       <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
       <c r="O38" s="4"/>
-      <c r="AA38" s="4"/>
-      <c r="AC38" s="4"/>
+      <c r="AB38" s="4"/>
       <c r="AD38" s="4"/>
       <c r="AE38" s="4"/>
-      <c r="AG38" s="4"/>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF38" s="4"/>
+      <c r="AH38" s="4"/>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3383,16 +3410,16 @@
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
       <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
       <c r="O39" s="4"/>
-      <c r="AA39" s="4"/>
-      <c r="AC39" s="4"/>
+      <c r="AB39" s="4"/>
       <c r="AD39" s="4"/>
       <c r="AE39" s="4"/>
-      <c r="AG39" s="4"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF39" s="4"/>
+      <c r="AH39" s="4"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3403,15 +3430,15 @@
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
       <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="AC40" s="4"/>
       <c r="AD40" s="4"/>
       <c r="AE40" s="4"/>
-      <c r="AG40" s="4"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF40" s="4"/>
+      <c r="AH40" s="4"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3422,15 +3449,15 @@
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
       <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
       <c r="O41" s="4"/>
-      <c r="AC41" s="4"/>
       <c r="AD41" s="4"/>
       <c r="AE41" s="4"/>
-      <c r="AG41" s="4"/>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF41" s="4"/>
+      <c r="AH41" s="4"/>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -3441,15 +3468,15 @@
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
       <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="AC42" s="4"/>
       <c r="AD42" s="4"/>
       <c r="AE42" s="4"/>
-      <c r="AG42" s="4"/>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF42" s="4"/>
+      <c r="AH42" s="4"/>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -3460,15 +3487,15 @@
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
       <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
       <c r="O43" s="4"/>
-      <c r="AC43" s="4"/>
       <c r="AD43" s="4"/>
       <c r="AE43" s="4"/>
-      <c r="AG43" s="4"/>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF43" s="4"/>
+      <c r="AH43" s="4"/>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -3479,40 +3506,40 @@
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
       <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="AC44" s="4"/>
       <c r="AD44" s="4"/>
       <c r="AE44" s="4"/>
-      <c r="AG44" s="4"/>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF44" s="4"/>
+      <c r="AH44" s="4"/>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="AC45" s="4"/>
       <c r="AD45" s="4"/>
       <c r="AE45" s="4"/>
-      <c r="AG45" s="4"/>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AF45" s="4"/>
+      <c r="AH45" s="4"/>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
-      <c r="AC46" s="4"/>
-      <c r="AE46" s="4"/>
-      <c r="AG46" s="4"/>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.15">
+      <c r="AD46" s="4"/>
+      <c r="AF46" s="4"/>
+      <c r="AH46" s="4"/>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411B48EF-300A-47A2-B468-DDD027F7F271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C255053-186E-4BF7-8507-6F456CB56863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="36" r:id="rId1"/>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C255053-186E-4BF7-8507-6F456CB56863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AFB532-C766-44A5-A34E-3D06DBF970EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AFB532-C766-44A5-A34E-3D06DBF970EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EB25C4-2760-4D7C-A439-CA455CC1F1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="132">
   <si>
     <t>备注:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -507,6 +507,10 @@
   </si>
   <si>
     <t>QRSLineMethod</t>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1400,7 +1404,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4">
         <v>5</v>
@@ -1957,7 +1961,7 @@
       <c r="AF13" s="4"/>
       <c r="AH13" s="4"/>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2173,7 +2177,7 @@
       <c r="AF16" s="4"/>
       <c r="AH16" s="4"/>
     </row>
-    <row r="17" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2244,7 +2248,7 @@
       <c r="AF17" s="4"/>
       <c r="AH17" s="4"/>
     </row>
-    <row r="18" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2315,7 +2319,7 @@
       <c r="AF18" s="4"/>
       <c r="AH18" s="4"/>
     </row>
-    <row r="19" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2387,7 +2391,7 @@
       <c r="AF19" s="4"/>
       <c r="AH19" s="4"/>
     </row>
-    <row r="20" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -2456,7 +2460,7 @@
       <c r="AF20" s="4"/>
       <c r="AH20" s="4"/>
     </row>
-    <row r="21" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -2528,7 +2532,7 @@
       <c r="AF21" s="4"/>
       <c r="AH21" s="4"/>
     </row>
-    <row r="22" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -2600,7 +2604,7 @@
       <c r="AF22" s="4"/>
       <c r="AH22" s="4"/>
     </row>
-    <row r="23" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -2672,7 +2676,7 @@
       <c r="AF23" s="4"/>
       <c r="AH23" s="4"/>
     </row>
-    <row r="24" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -2744,7 +2748,7 @@
       <c r="AF24" s="4"/>
       <c r="AH24" s="4"/>
     </row>
-    <row r="25" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -2816,7 +2820,7 @@
       <c r="AF25" s="4"/>
       <c r="AH25" s="4"/>
     </row>
-    <row r="26" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -2829,8 +2833,12 @@
       <c r="E26" s="4">
         <v>3</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="F26" s="4">
+        <v>1</v>
+      </c>
+      <c r="G26" s="4">
+        <v>15</v>
+      </c>
       <c r="H26" s="4">
         <v>10</v>
       </c>
@@ -2882,7 +2890,7 @@
       <c r="AF26" s="4"/>
       <c r="AH26" s="4"/>
     </row>
-    <row r="27" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -2948,7 +2956,10 @@
       <c r="AF27" s="4"/>
       <c r="AH27" s="4"/>
     </row>
-    <row r="28" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="A28" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -2961,7 +2972,9 @@
       <c r="E28" s="4">
         <v>3</v>
       </c>
-      <c r="F28" s="4"/>
+      <c r="F28" s="4">
+        <v>1</v>
+      </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4">
         <v>15</v>
@@ -2976,7 +2989,7 @@
         <v>107</v>
       </c>
       <c r="M28" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N28" s="4">
         <v>0</v>
@@ -3014,7 +3027,7 @@
       <c r="AF28" s="4"/>
       <c r="AH28" s="4"/>
     </row>
-    <row r="29" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3027,7 +3040,9 @@
       <c r="E29" s="4">
         <v>3</v>
       </c>
-      <c r="F29" s="4"/>
+      <c r="F29" s="4">
+        <v>1</v>
+      </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4">
         <v>15</v>
@@ -3042,7 +3057,7 @@
         <v>108</v>
       </c>
       <c r="M29" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N29" s="4">
         <v>0</v>
@@ -3081,7 +3096,7 @@
       <c r="AF29" s="4"/>
       <c r="AH29" s="4"/>
     </row>
-    <row r="30" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3109,7 +3124,7 @@
         <v>109</v>
       </c>
       <c r="M30" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N30" s="4">
         <v>0</v>
@@ -3148,7 +3163,7 @@
       <c r="AF30" s="4"/>
       <c r="AH30" s="4"/>
     </row>
-    <row r="31" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -3161,7 +3176,9 @@
       <c r="E31" s="4">
         <v>3</v>
       </c>
-      <c r="F31" s="4"/>
+      <c r="F31" s="4">
+        <v>35</v>
+      </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4">
         <v>10</v>
@@ -3212,7 +3229,7 @@
       <c r="AF31" s="4"/>
       <c r="AH31" s="4"/>
     </row>
-    <row r="32" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -3225,7 +3242,9 @@
       <c r="E32" s="4">
         <v>3</v>
       </c>
-      <c r="F32" s="4"/>
+      <c r="F32" s="4">
+        <v>2</v>
+      </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4">
         <v>20</v>
@@ -3290,9 +3309,6 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
-      <c r="U33" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="AB33" s="4"/>
       <c r="AD33" s="4"/>
       <c r="AE33" s="4"/>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EB25C4-2760-4D7C-A439-CA455CC1F1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F8309F-DADB-4C30-BF21-20459D9AFEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H20" s="4">
         <v>10</v>
@@ -2477,7 +2477,7 @@
         <v>20</v>
       </c>
       <c r="G21" s="4">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="H21" s="4">
         <v>15</v>
@@ -2549,7 +2549,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="4">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H22" s="4">
         <v>20</v>
@@ -2765,7 +2765,7 @@
         <v>35</v>
       </c>
       <c r="G25" s="4">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H25" s="4">
         <v>20</v>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F8309F-DADB-4C30-BF21-20459D9AFEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C890752F-99B6-4DB7-9889-9620AEFD6DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="36" r:id="rId1"/>
@@ -995,38 +995,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AI69"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.25" style="2" customWidth="1"/>
-    <col min="11" max="11" width="21.875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="22.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.453125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.26953125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="21.90625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="22.6328125" style="2" customWidth="1"/>
     <col min="13" max="13" width="17" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="255.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="255.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.75" style="2" customWidth="1"/>
-    <col min="22" max="22" width="20.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7265625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="17" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="22" style="2" bestFit="1" customWidth="1"/>
     <col min="25" max="27" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="18.25" style="2" customWidth="1"/>
-    <col min="29" max="29" width="70.5" style="2" customWidth="1"/>
+    <col min="28" max="28" width="18.26953125" style="2" customWidth="1"/>
+    <col min="29" max="29" width="70.453125" style="2" customWidth="1"/>
     <col min="30" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11"/>
       <c r="B1" s="12" t="s">
         <v>9</v>
@@ -1113,7 +1113,7 @@
       <c r="AH1" s="8"/>
       <c r="AI1" s="6"/>
     </row>
-    <row r="2" spans="1:35" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:35" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1152,7 +1152,7 @@
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
     </row>
-    <row r="3" spans="1:35" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:35" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1241,7 +1241,7 @@
       <c r="AH3" s="7"/>
       <c r="AI3" s="7"/>
     </row>
-    <row r="4" spans="1:35" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:35" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB4" s="15"/>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1391,7 +1391,7 @@
       <c r="AF5" s="4"/>
       <c r="AH5" s="4"/>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1458,7 +1458,7 @@
       <c r="AF6" s="4"/>
       <c r="AH6" s="4"/>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1532,7 +1532,7 @@
       <c r="AF7" s="4"/>
       <c r="AH7" s="4"/>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1603,7 +1603,7 @@
       <c r="AF8" s="4"/>
       <c r="AH8" s="4"/>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -1677,7 +1677,7 @@
       <c r="AF9" s="4"/>
       <c r="AH9" s="4"/>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -1748,7 +1748,7 @@
       <c r="AF10" s="4"/>
       <c r="AH10" s="4"/>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -1819,7 +1819,7 @@
       <c r="AF11" s="4"/>
       <c r="AH11" s="4"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -1890,7 +1890,7 @@
       <c r="AF12" s="4"/>
       <c r="AH12" s="4"/>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -1961,7 +1961,7 @@
       <c r="AF13" s="4"/>
       <c r="AH13" s="4"/>
     </row>
-    <row r="14" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2035,7 +2035,7 @@
       <c r="AF14" s="4"/>
       <c r="AH14" s="4"/>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2106,7 +2106,7 @@
       <c r="AF15" s="4"/>
       <c r="AH15" s="4"/>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2177,7 +2177,7 @@
       <c r="AF16" s="4"/>
       <c r="AH16" s="4"/>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2248,7 +2248,7 @@
       <c r="AF17" s="4"/>
       <c r="AH17" s="4"/>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2319,7 +2319,7 @@
       <c r="AF18" s="4"/>
       <c r="AH18" s="4"/>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2333,10 +2333,10 @@
         <v>2</v>
       </c>
       <c r="F19" s="4">
+        <v>50</v>
+      </c>
+      <c r="G19" s="4">
         <v>15</v>
-      </c>
-      <c r="G19" s="4">
-        <v>20</v>
       </c>
       <c r="H19" s="4">
         <v>15</v>
@@ -2391,7 +2391,7 @@
       <c r="AF19" s="4"/>
       <c r="AH19" s="4"/>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -2460,7 +2460,7 @@
       <c r="AF20" s="4"/>
       <c r="AH20" s="4"/>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -2532,7 +2532,7 @@
       <c r="AF21" s="4"/>
       <c r="AH21" s="4"/>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -2604,7 +2604,7 @@
       <c r="AF22" s="4"/>
       <c r="AH22" s="4"/>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -2676,7 +2676,7 @@
       <c r="AF23" s="4"/>
       <c r="AH23" s="4"/>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -2748,7 +2748,7 @@
       <c r="AF24" s="4"/>
       <c r="AH24" s="4"/>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -2820,7 +2820,7 @@
       <c r="AF25" s="4"/>
       <c r="AH25" s="4"/>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -2890,7 +2890,7 @@
       <c r="AF26" s="4"/>
       <c r="AH26" s="4"/>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -2956,7 +2956,7 @@
       <c r="AF27" s="4"/>
       <c r="AH27" s="4"/>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>131</v>
       </c>
@@ -3027,7 +3027,7 @@
       <c r="AF28" s="4"/>
       <c r="AH28" s="4"/>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3096,7 +3096,7 @@
       <c r="AF29" s="4"/>
       <c r="AH29" s="4"/>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3163,7 +3163,7 @@
       <c r="AF30" s="4"/>
       <c r="AH30" s="4"/>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -3229,7 +3229,7 @@
       <c r="AF31" s="4"/>
       <c r="AH31" s="4"/>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -3295,7 +3295,7 @@
       <c r="AF32" s="4"/>
       <c r="AH32" s="4"/>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -3315,7 +3315,7 @@
       <c r="AF33" s="4"/>
       <c r="AH33" s="4"/>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -3335,7 +3335,7 @@
       <c r="AF34" s="4"/>
       <c r="AH34" s="4"/>
     </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -3355,7 +3355,7 @@
       <c r="AF35" s="4"/>
       <c r="AH35" s="4"/>
     </row>
-    <row r="36" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -3375,7 +3375,7 @@
       <c r="AF36" s="4"/>
       <c r="AH36" s="4"/>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -3395,7 +3395,7 @@
       <c r="AF37" s="4"/>
       <c r="AH37" s="4"/>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -3415,7 +3415,7 @@
       <c r="AF38" s="4"/>
       <c r="AH38" s="4"/>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3435,7 +3435,7 @@
       <c r="AF39" s="4"/>
       <c r="AH39" s="4"/>
     </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3454,7 +3454,7 @@
       <c r="AF40" s="4"/>
       <c r="AH40" s="4"/>
     </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3473,7 +3473,7 @@
       <c r="AF41" s="4"/>
       <c r="AH41" s="4"/>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -3492,7 +3492,7 @@
       <c r="AF42" s="4"/>
       <c r="AH42" s="4"/>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -3511,7 +3511,7 @@
       <c r="AF43" s="4"/>
       <c r="AH43" s="4"/>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -3530,7 +3530,7 @@
       <c r="AF44" s="4"/>
       <c r="AH44" s="4"/>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -3540,7 +3540,7 @@
       <c r="AF45" s="4"/>
       <c r="AH45" s="4"/>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -3549,139 +3549,139 @@
       <c r="AF46" s="4"/>
       <c r="AH46" s="4"/>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B69" s="4"/>
     </row>
   </sheetData>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C890752F-99B6-4DB7-9889-9620AEFD6DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53282414-7544-4F7F-B775-9954824E3257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,415 +101,416 @@
     <t>突刺</t>
   </si>
   <si>
+    <t>熊手</t>
+  </si>
+  <si>
+    <t>横扫</t>
+  </si>
+  <si>
+    <t>旋风</t>
+  </si>
+  <si>
+    <t>火矢</t>
+  </si>
+  <si>
+    <t>贯箭</t>
+  </si>
+  <si>
+    <t>乱射</t>
+  </si>
+  <si>
+    <t>突破</t>
+  </si>
+  <si>
+    <t>突进</t>
+  </si>
+  <si>
+    <t>破碎</t>
+  </si>
+  <si>
+    <t>放射</t>
+  </si>
+  <si>
+    <t>猛撞</t>
+  </si>
+  <si>
+    <t>costEnergy</t>
+  </si>
+  <si>
+    <t>isRange</t>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击额外位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>近战普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远程普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkDurability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canDamageMachine</t>
+  </si>
+  <si>
+    <t>canDamageBoat</t>
+  </si>
+  <si>
+    <t>canDamageTeam</t>
+  </si>
+  <si>
+    <t>误伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>戟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canDamageTroop</t>
+  </si>
+  <si>
+    <t>攻击部队</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spellRanges</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkOffsetPoint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否远程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>井阑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木兽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投石船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艨艟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canDamageBuilding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二段突刺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blockFactor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击附加效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillEffects</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offsetAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>位移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,-1,2,-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2,1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础成功率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>successRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>needAblilityLevel</t>
+  </si>
+  <si>
+    <t>必要兵装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>needItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标撞击伤害倍率(百分比)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aobj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扰乱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伪报</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灭火</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>镇静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伏兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内讧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canSpellToCell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onlySpellToTeam</t>
+  </si>
+  <si>
+    <t>successMethod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>criticalMethod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功率逻辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率逻辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CommonMethod</t>
+  </si>
+  <si>
+    <t>PutOutFireCriticalMethod</t>
+  </si>
+  <si>
+    <t>FalseReportCriticalMethod</t>
+  </si>
+  <si>
+    <t>DisturbCriticalMethod</t>
+  </si>
+  <si>
+    <t>CalmdownCriticalMethod</t>
+  </si>
+  <si>
+    <t>AmbushCriticalMethod</t>
+  </si>
+  <si>
+    <t>PutOutFireSuccessMethod</t>
+  </si>
+  <si>
+    <t>FalseReportSuccessMethod</t>
+  </si>
+  <si>
+    <t>DisturbSuccessMethod</t>
+  </si>
+  <si>
+    <t>CalmdownSuccessMethod</t>
+  </si>
+  <si>
+    <t>AmbushSuccessMethod</t>
+  </si>
+  <si>
+    <t>InfightingSuccessMethod</t>
+  </si>
+  <si>
+    <t>InfightingCriticalMethod</t>
+  </si>
+  <si>
+    <t>FireCriticalMethod</t>
+  </si>
+  <si>
+    <t>[{class:"PutoutFire",probability:10000}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"AddBuff",buffId:2,probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:2,probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+  </si>
+  <si>
+    <t>[{class:"AddBuff",buffId:1,probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:1,probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CommonMethod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"RemoveBuffById",values:[1,2],probability:10000},{class:"RecureWoundedTroops",probability:10000,values:[20,30], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"SetFire",probability:5000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"SetFire",probability:5000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"SetFire",probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"SetFire",probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>射程筛选逻辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rangeFilterMethod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FireSuccessMethod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QRSLineMethod</t>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"AddBuff",buffId:1,probability:5000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:1,probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>螺旋突刺</t>
-  </si>
-  <si>
-    <t>熊手</t>
-  </si>
-  <si>
-    <t>横扫</t>
-  </si>
-  <si>
-    <t>旋风</t>
-  </si>
-  <si>
-    <t>火矢</t>
-  </si>
-  <si>
-    <t>贯箭</t>
-  </si>
-  <si>
-    <t>乱射</t>
-  </si>
-  <si>
-    <t>突破</t>
-  </si>
-  <si>
-    <t>突进</t>
-  </si>
-  <si>
-    <t>破碎</t>
-  </si>
-  <si>
-    <t>放射</t>
-  </si>
-  <si>
-    <t>猛撞</t>
-  </si>
-  <si>
-    <t>costEnergy</t>
-  </si>
-  <si>
-    <t>isRange</t>
-  </si>
-  <si>
-    <t>Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击额外位置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>近战普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>远程普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkDurability</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>canDamageMachine</t>
-  </si>
-  <si>
-    <t>canDamageBoat</t>
-  </si>
-  <si>
-    <t>canDamageTeam</t>
-  </si>
-  <si>
-    <t>误伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>枪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>戟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>骑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>canDamageTroop</t>
-  </si>
-  <si>
-    <t>攻击部队</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spellRanges</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkOffsetPoint</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否远程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>井阑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冲车</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>木兽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>投石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小船</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>投石船</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>艨艟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>canDamageBuilding</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>二段突刺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>blockFactor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击附加效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>突击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skillEffects</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>offsetAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>位移</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,-1,2,-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,1,1,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,2,1,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础成功率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>successRate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>needAblilityLevel</t>
-  </si>
-  <si>
-    <t>必要兵装</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>needItem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kind</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标撞击伤害倍率(百分比)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aobj</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>扰乱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伪报</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计略</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>灭火</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>镇静</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伏兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内讧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>canSpellToCell</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>onlySpellToTeam</t>
-  </si>
-  <si>
-    <t>successMethod</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>criticalMethod</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>成功率逻辑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击率逻辑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CommonMethod</t>
-  </si>
-  <si>
-    <t>PutOutFireCriticalMethod</t>
-  </si>
-  <si>
-    <t>FalseReportCriticalMethod</t>
-  </si>
-  <si>
-    <t>DisturbCriticalMethod</t>
-  </si>
-  <si>
-    <t>CalmdownCriticalMethod</t>
-  </si>
-  <si>
-    <t>AmbushCriticalMethod</t>
-  </si>
-  <si>
-    <t>PutOutFireSuccessMethod</t>
-  </si>
-  <si>
-    <t>FalseReportSuccessMethod</t>
-  </si>
-  <si>
-    <t>DisturbSuccessMethod</t>
-  </si>
-  <si>
-    <t>CalmdownSuccessMethod</t>
-  </si>
-  <si>
-    <t>AmbushSuccessMethod</t>
-  </si>
-  <si>
-    <t>InfightingSuccessMethod</t>
-  </si>
-  <si>
-    <t>InfightingCriticalMethod</t>
-  </si>
-  <si>
-    <t>FireCriticalMethod</t>
-  </si>
-  <si>
-    <t>[{class:"PutoutFire",probability:10000}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"AddBuff",buffId:1,probability:5000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:1,probability:5000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"AddBuff",buffId:2,probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:2,probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-  </si>
-  <si>
-    <t>[{class:"AddBuff",buffId:1,probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:1,probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CommonMethod</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"RemoveBuffById",values:[1,2],probability:10000},{class:"RecureWoundedTroops",probability:10000,values:[20,30], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"SetFire",probability:5000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"SetFire",probability:5000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"SetFire",probability:10000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"SetFire",probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>射程筛选逻辑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rangeFilterMethod</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FireSuccessMethod</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QRSLineMethod</t>
-  </si>
-  <si>
-    <t>2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1036,7 +1037,7 @@
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>11</v>
@@ -1048,16 +1049,16 @@
         <v>13</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J1" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="K1" s="12" t="s">
-        <v>104</v>
-      </c>
       <c r="L1" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M1" s="12" t="s">
         <v>14</v>
@@ -1066,25 +1067,25 @@
         <v>18</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R1" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="T1" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U1" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V1" s="12" t="s">
         <v>15</v>
@@ -1096,13 +1097,13 @@
         <v>17</v>
       </c>
       <c r="Y1" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z1" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA1" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB1" s="12"/>
       <c r="AC1" s="6"/>
@@ -1157,80 +1158,80 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="V3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="V3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="X3" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="X3" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y3" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="Z3" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA3" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="AA3" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
@@ -1246,46 +1247,46 @@
         <v>1</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M4" s="13" t="s">
         <v>4</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P4" s="13" t="s">
         <v>8</v>
@@ -1294,13 +1295,13 @@
         <v>4</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S4" s="13" t="s">
         <v>4</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U4" s="13" t="s">
         <v>8</v>
@@ -1330,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4">
@@ -1349,10 +1350,10 @@
         <v>100</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M5" s="4">
         <v>1</v>
@@ -1397,7 +1398,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4">
@@ -1416,10 +1417,10 @@
         <v>100</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M6" s="4">
         <v>2</v>
@@ -1466,7 +1467,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="4">
         <v>2</v>
@@ -1484,10 +1485,10 @@
         <v>70</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M7" s="4">
         <v>1</v>
@@ -1500,10 +1501,10 @@
         <v>7</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>6</v>
@@ -1537,10 +1538,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" s="4">
         <v>2</v>
@@ -1558,10 +1559,10 @@
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M8" s="4">
         <v>1</v>
@@ -1574,7 +1575,7 @@
         <v>7</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>6</v>
@@ -1608,10 +1609,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" s="4">
         <v>2</v>
@@ -1629,10 +1630,10 @@
         <v>60</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M9" s="4">
         <v>1</v>
@@ -1645,10 +1646,10 @@
         <v>7</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>6</v>
@@ -1682,10 +1683,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" s="4">
         <v>2</v>
@@ -1703,10 +1704,10 @@
         <v>70</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M10" s="4">
         <v>1</v>
@@ -1719,7 +1720,7 @@
         <v>7</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>6</v>
@@ -1753,10 +1754,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" s="4">
         <v>2</v>
@@ -1774,10 +1775,10 @@
         <v>70</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M11" s="4">
         <v>1</v>
@@ -1790,7 +1791,7 @@
         <v>7</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>6</v>
@@ -1824,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12" s="4">
         <v>2</v>
@@ -1845,10 +1846,10 @@
         <v>65</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M12" s="4">
         <v>1</v>
@@ -1861,7 +1862,7 @@
         <v>7</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="U12" s="2" t="s">
         <v>6</v>
@@ -1895,10 +1896,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" s="4">
         <v>2</v>
@@ -1916,10 +1917,10 @@
         <v>75</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M13" s="4">
         <v>2</v>
@@ -1932,7 +1933,7 @@
         <v>6</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="U13" s="2" t="s">
         <v>6</v>
@@ -1966,10 +1967,10 @@
         <v>10</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" s="4">
         <v>2</v>
@@ -1987,13 +1988,13 @@
         <v>70</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M14" s="4">
         <v>2</v>
@@ -2006,7 +2007,7 @@
         <v>6</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U14" s="2" t="s">
         <v>6</v>
@@ -2040,10 +2041,10 @@
         <v>11</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" s="4">
         <v>2</v>
@@ -2061,10 +2062,10 @@
         <v>65</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M15" s="4">
         <v>2</v>
@@ -2077,7 +2078,7 @@
         <v>6</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U15" s="2" t="s">
         <v>6</v>
@@ -2111,10 +2112,10 @@
         <v>12</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" s="4">
         <v>2</v>
@@ -2132,10 +2133,10 @@
         <v>70</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M16" s="4">
         <v>1</v>
@@ -2148,7 +2149,7 @@
         <v>7</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U16" s="2" t="s">
         <v>6</v>
@@ -2182,10 +2183,10 @@
         <v>13</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" s="4">
         <v>2</v>
@@ -2203,10 +2204,10 @@
         <v>65</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M17" s="4">
         <v>1</v>
@@ -2219,7 +2220,7 @@
         <v>7</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U17" s="2" t="s">
         <v>6</v>
@@ -2253,10 +2254,10 @@
         <v>14</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" s="4">
         <v>2</v>
@@ -2274,10 +2275,10 @@
         <v>60</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M18" s="4">
         <v>1</v>
@@ -2290,7 +2291,7 @@
         <v>7</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U18" s="2" t="s">
         <v>6</v>
@@ -2324,10 +2325,10 @@
         <v>15</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E19" s="4">
         <v>2</v>
@@ -2345,10 +2346,10 @@
         <v>100</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M19" s="4">
         <v>2</v>
@@ -2363,7 +2364,7 @@
         <v>6</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="U19" s="2" t="s">
         <v>6</v>
@@ -2396,10 +2397,10 @@
         <v>16</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E20" s="4">
         <v>2</v>
@@ -2417,10 +2418,10 @@
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M20" s="4">
         <v>1</v>
@@ -2465,10 +2466,10 @@
         <v>17</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E21" s="4">
         <v>2</v>
@@ -2486,10 +2487,10 @@
         <v>100</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M21" s="4">
         <v>1</v>
@@ -2504,7 +2505,7 @@
         <v>6</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="U21" s="2" t="s">
         <v>6</v>
@@ -2540,7 +2541,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E22" s="4">
         <v>2</v>
@@ -2558,13 +2559,13 @@
         <v>100</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N22" s="4">
         <v>0</v>
@@ -2576,7 +2577,7 @@
         <v>6</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U22" s="2" t="s">
         <v>6</v>
@@ -2609,10 +2610,10 @@
         <v>19</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" s="4">
         <v>2</v>
@@ -2630,10 +2631,10 @@
         <v>100</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M23" s="4">
         <v>2</v>
@@ -2648,7 +2649,7 @@
         <v>6</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="U23" s="2" t="s">
         <v>6</v>
@@ -2681,10 +2682,10 @@
         <v>20</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" s="4">
         <v>2</v>
@@ -2702,10 +2703,10 @@
         <v>70</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M24" s="4">
         <v>1</v>
@@ -2720,7 +2721,7 @@
         <v>7</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U24" s="2" t="s">
         <v>6</v>
@@ -2756,7 +2757,7 @@
         <v>3</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E25" s="4">
         <v>2</v>
@@ -2774,13 +2775,13 @@
         <v>100</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N25" s="4">
         <v>3</v>
@@ -2792,7 +2793,7 @@
         <v>6</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U25" s="2" t="s">
         <v>6</v>
@@ -2825,10 +2826,10 @@
         <v>22</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E26" s="4">
         <v>3</v>
@@ -2846,10 +2847,10 @@
         <v>0</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M26" s="4">
         <v>1</v>
@@ -2862,7 +2863,7 @@
         <v>6</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="U26" s="2" t="s">
         <v>6</v>
@@ -2895,10 +2896,10 @@
         <v>23</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E27" s="4">
         <v>3</v>
@@ -2912,10 +2913,10 @@
         <v>0</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M27" s="4">
         <v>1</v>
@@ -2928,7 +2929,7 @@
         <v>6</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U27" s="2" t="s">
         <v>6</v>
@@ -2958,16 +2959,16 @@
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B28" s="4">
         <v>24</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="E28" s="4">
         <v>3</v>
@@ -2983,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M28" s="4">
         <v>2</v>
@@ -2999,7 +3000,7 @@
         <v>6</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="U28" s="2" t="s">
         <v>6</v>
@@ -3032,10 +3033,10 @@
         <v>25</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E29" s="4">
         <v>3</v>
@@ -3051,10 +3052,10 @@
         <v>0</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M29" s="4">
         <v>2</v>
@@ -3067,7 +3068,7 @@
         <v>6</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="U29" s="2" t="s">
         <v>6</v>
@@ -3101,10 +3102,10 @@
         <v>26</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E30" s="4">
         <v>3</v>
@@ -3118,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M30" s="4">
         <v>2</v>
@@ -3134,7 +3135,7 @@
         <v>6</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="U30" s="2" t="s">
         <v>6</v>
@@ -3168,10 +3169,10 @@
         <v>27</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E31" s="4">
         <v>3</v>
@@ -3187,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M31" s="4">
         <v>1</v>
@@ -3234,10 +3235,10 @@
         <v>28</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E32" s="4">
         <v>3</v>
@@ -3253,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="J32" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K32" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>117</v>
       </c>
       <c r="M32" s="4">
         <v>1</v>
